--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
@@ -422,17 +422,17 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -603,14 +603,22 @@
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L113: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: of any subsÃ©quent stage of the cause, the plaintiff seems</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE " PRO CONFESSO."</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE " PRO CONFESSO."</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L11: isolated marker/symbol line :: 0</t>
@@ -626,7 +634,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L96: line starts with punctuation glued to text :: .In cases where a decree is not absolute under order</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tunity to Court within the time specified in such notice, or that such</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,10 +670,14 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L174: stray/suspicious non-ASCII glyph(s): U+221A SQUARE ROOT | isolated marker/symbol line :: √</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ tunity to Court within the time specified in such notice, or that such</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tunity to Court within the time specified in such notice, or that such</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -679,7 +691,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L96: line starts with punctuation glued to text :: .In cases where a decree is not absolute under order</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -738,7 +754,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -930,7 +946,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: m</t>
+          <t>L113: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -953,7 +969,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -973,7 +989,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L162: isolated marker/symbol line :: 0</t>
+          <t>L154: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1001,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1016,7 +1032,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L175: isolated marker/symbol line :: -</t>
+          <t>L162: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1039,7 +1055,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1057,7 +1073,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L174: stray/suspicious non-ASCII glyph(s): U+221A SQUARE ROOT | isolated marker/symbol line :: √</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1096,7 +1116,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L175: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1122,7 +1146,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
